--- a/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 몇 달째 남편 가족이 하고 있는 일을 사람들이 진지하게 받아들여 주게 하려고 애써왔는데, 그래서 오게 됐어요. 그 사람들이 조용히 우리 돈이랑 평판을 흔들고 있어요. 그러니까, 직장에서 작은 청구 실수가 생기거나, 교회에서 누가 갑자기 저한테 이상하게 행동하거나 하는데, 사람들은 증거가 없다거나 기록에는 아무것도 안 나온다고 해요. 근데 저는 그게 다 그 집안이랑 연결돼 있다는 걸 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 다른 사람들도 남편 가족과 이런 일들 사이의 연관성을 알아차릴 수 있다고 생각하시나요, 아니면 본인만 그걸 눈치채고 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 제가 거의 유일하게 그걸 명확히 보고 있는 것 같아요. 다른 사람들도 조각조각은 눈치채요, 청구 오류라든가 교회에서 누가 다르게 행동하는 거라든가. 근데 그걸 하나로 연결해서 보려고는 안 해요. 기록에는 아무것도 안 나온다고들 하는데, 저는 남편 가족이 그 뒤에 있다는 걸 알아요. 그 사람들은 조심스럽게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 남편 가족이 본인을 향한 행동을 공개적으로 얘기하고 다닌다고 생각하시나요, 아니면 몰래 하고 있는 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 공개적으로 말하지는 않아요. 그게 바로 문제예요—조용히 하고 있어서 겉으로 보면 그냥 작은 실수나 사람들이 괜히 다르게 행동하는 걸로 보여요. 근데 저는 그게 그 사람들 짓이라는 걸 알아요, 특히 돈 문제랑 우리 이름이 사람들 입에 오르내리는 방식을 보면요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 만약 남편 가족에게 직접 물어보면 이런 일들을 했다고 인정할 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 인정하지 않을 거예요. 제가 그냥 지어내는 거라거나 단순한 실수라고 할 거예요, 그래야 조용히 넘어갈 수 있으니까요. 근데 저는 돈 문제랑 사람들이 저를 대하는 방식에서 무슨 일이 있었는지 알고 있고, 그건 다 그 집안으로 이어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 남편 가족에 대한 본인의 믿음에 대해 의심이 든 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 별로 없어요. 그러니까, 공정하게 다른 사람들 말도 들어보려고 하긴 하는데, 몇 달 동안 이런 일들—청구 오류, 교회에서 사람들이 다르게 행동하는 거, 우리 이름이 오르내리는 거—이 계속되고 나니까 우연으로 느껴지지가 않아요. 기록에 뚜렷하게 안 나와도 저는 여전히 그게 남편 가족이랑 이어져 있다는 걸 알아요. 그 사람들은 그냥 조심스럽게 하는 것뿐이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 아무리 작은 가능성이라도, 이 일들의 배후에 남편 가족이 없을 가능성이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 솔직히 아니요, 그럴 가능성은 별로 없다고 생각해요. 다른 방식으로 보려고 해봤는데, 몇 달째 같은 패턴이에요—작은 청구 문제들, 교회에서 사람들이 이상하게 행동하는 거, 우리 이름에 대해 이런저런 말이 나오는 거요. 누가 기록을 보여주면서 그런 거 안 보인다고 해도, 저는 그게 남편 가족으로 이어진다는 걸 알아요. 그냥 조용히 하고 있는 것뿐이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 남편 가족이 이 일들의 배후에 있다고 믿지 않았던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없어요. 시작된 이후로 계속 저한테는 분명했어요. 몇 달째 그 사람들이 조용히 우리 돈이랑 좋은 평판을 흔들고 있다는 걸 사람들이 이해하게 하려고 애써왔어요. 작은 청구 오류라든가, 교회에서 갑자기 사람들이 저한테 다르게 구는 거요… 누가 기록을 확인해 보고 아무것도 안 보인다고 해도, 저는 여전히 그게 그 사람들이랑 연결돼 있다는 걸 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 남편 가족이 하고 있다고 믿는 일들이 실제로 일어날 수 있는 일이라고 보시나요, 아니면 매우 이례적인 일이라고 보시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 실제로 일어날 수 있는 일이라고 생각해요. 그러니까, 사람들이 돈에 관여하거나, 작은 일들이 잘못되게 만들거나, 다른 사람들에게 당신 이름에 대해 이야기하거나 할 수 있잖아요. 제가 불가능한 얘기를 하는 게 아니에요. 그냥 조용히 이루어지고 있어서, 기록을 봐도 다른 사람들이 알아차리기 힘든 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 남편 가족이 이 일들의 배후에 있다고 믿은 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 이제 아홉 달쯤 됐어요. 돈이랑 명절 기대치 문제로 남편 가족이랑 그 다툼이 있고 나서 시작됐고, 그 이후로 그 사람들이 배후에 있다고 믿게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 본인은 사실이라고 생각하지만 다른 사람들은 믿기 힘들어할 만한 다른 믿음이 또 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 다른 건 별로 없어요. 주로 남편 가족 관련 이 일이에요. 다른 사람들이 제가 너무 지나치게 생각한다고 여기는 건 알지만, 청구 오류가 생기거나 교회에서 사람들이 저한테 이상하게 구는 걸 보면, 그냥 우연이라고 보기가 힘들어요. 누가 기록을 확인해서 아무것도 없다고 해도, 저는 여전히 그게 그 사람들이랑 연결돼 있다고 믿어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 지난 아홉 달 동안 남편 가족이 이 일들의 배후에 있다는 믿음이 바뀌거나 흔들린 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 아니요, 별로요. 그러니까, 그냥 넘기려고 스스로 다독여본 적은 있을지도 모르는데, 비슷한 일들이 계속 반복돼서 다시 떠올라요. 청구 오류, 교회에서 사람들이 저한테 다르게 구는 거… 다른 사람들이 기록에 안 나온다고 해도 다 남편 가족을 가리키는 것 같아요. 그러니까 딱히 흔들렸다고는 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 남편 가족에 대한 본인의 믿음이 사실이 아닐 가능성을 고려해 본 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 사람들이 계속 제가 틀렸다고 할 때 아주 잠깐씩은요. 그냥 청구 실수일 수도 있고 아니면 교회에서 누가 그날 기분이 안 좋았을 뿐일 수도 있다고 생각해 보려고 했어요. 근데 비슷한 작은 일들이 계속 일어나고, 그게 너무 연관돼 있는 것처럼 느껴져요. 사람들이 무슨 기록을 가져와도, 저는 여전히 그게 남편 가족이 우리 돈이랑 이름을 가지고 문제를 일으키는 것과 이어져 있다고 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 남편 가족 말고 다른 사람들이 본인을 노리거나 감시하고 있다고 느낀 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 그 사람들 말고는 별로 없어요. 그러니까, 교회에서 사람들이 이상하게 굴거나 작은 청구 오류가 생기는 건 있는데, 그게 무작위의 사람들이 저를 감시하거나 쫓아다닌다고는 생각 안 해요. 저한테는 다 남편 가족이 조용히 우리 돈이랑 좋은 평판에 문제를 일으키는 걸로 귀결돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 본인은 완전히 확신하지만 다른 사람들은 동의하지 않았던 생각이나 믿음이 또 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 아니요, 딱히 그런 다른 믿음은 없어요. 주로 남편 가족 관련 이 한 가지예요. 그 사람들이 조용히 우리 돈이랑 평판에 문제를 일으키고 있다고 확신해요—청구 문제라든가 교회에서 사람들이 저를 대하는 방식이요. 다른 사람들은 동의 안 하거나 기록에 안 나온다고 하지만, 저는 그게 그 사람들이랑 연결돼 있다는 걸 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 아홉 달 전 이 일들을 처음 알아차렸을 때부터 남편 가족에 대한 믿음이 조금이라도 바뀌었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 딱히 바뀌진 않았어요. 오히려 이 몇 달 동안 비슷한 일들이 계속 반복되면서—작은 청구 오류, 교회에서 사람들이 다르게 구는 것—더 확신하게 됐어요. 누가 기록을 보여주거나 아무것도 증명 안 된다고 해도, 저는 여전히 그게 남편 가족이 우리 돈이랑 이름을 흔드는 걸로 이어진다는 걸 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 완전히 확신했지만 다른 사람들에게는 이상하거나 있을 법하지 않게 느껴졌던 다른 생각이나 믿음이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 아니요, 다른 건 별로 없어요. 계속 말씀드린 이 상황 그대로예요—남편 가족이 조용히 우리 돈이랑 좋은 이름에 문제를 일으키는 거요. 청구 오류라든가 교회에서 사람들이 저한테 이상하게 구는 거요. 다른 사람들은 기록에 안 나온다고 하지만, 저는 그게 그 사람들이랑 이어져 있다는 걸 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 아홉 달 동안 남편 가족이 이 일들의 배후에 있다는 확신이 약해진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 아니요, 별로 약해지지 않았어요. 사람들이 저처럼 보지 않는다는 건 알고, 기록을 가져와서 증거가 없다고 하는 것도 알지만, 저한테는 여전히 그게 맞아떨어져요. 청구 실수들, 교회에서 사람들이 다르게 구는 거… 저는 여전히 남편 가족이 그 배후에서 조용히 우리 돈이랑 이름에 피해를 주고 있다고 믿어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 다른 사람들은 듣거나 보지 못하는 목소리를 듣거나 뭔가를 본 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그런 목소리나 장면을 본 적은 없어요. 그냥 제 주변에서 일어나는 일들을 눈치채는 것뿐이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 아주 강하게 믿었던 것이 나중에 사실이 아니었던 것으로 밝혀진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그러니까, 사람들이 계속 이게 사실이 아니라거나 기록에 아무것도 안 나온다고 하지만, 저는 여전히 무슨 일이 일어나고 있는지 알아요. 몇 달째 남편 가족이 조용히 우리 돈이랑 평판을 흔들고 있다는 걸 설명하려고 애써왔어요—작은 청구 오류라든가 교회에서 몇몇 사람들이 저한테 이상하게 구는 것처럼요. 그게 나중에 거짓으로 밝혀진 거라고는 생각 안 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 망상장애 (D004)
 인구통계: 성별 여성 / 나이 47 / 직업상태 billing or posting clerk / 최종학력 고등학교 졸업
@@ -575,467 +978,29 @@
 증상 지속 기간: 9 months
 추가 요건: Functioning is not markedly impaired apart from the impact of the delusion(s) or its ramifications
 주호소 증상 코드: S019
-배경 서술: 페기와 배우자의 친척들 사이의 관계는 돈, 집안일 분담, 명절 모임에 대한 기대를 둘러싼 다툼 이후 껄끄러워졌다. 그 후 9개월 동안, 평범한 가족 간의 오해와 직장에서의 청구 오류가 페기의 머릿속에서 시댁 식구들이 자신들의 평판과 재정적 안정을 흔들려 한다는 고정된 믿음과 연결되었고, 은행 기록과 동료들, 배우자가 그 반대 증거를 제시해도 흔들리지 않았다. 그 확신이 페기가 평소의 사무직 업무나 정원 가꾸기, 그림 그리기를 하는 것을 막지는 않았지만, 가정과 교회 모임에서 반복적인 충돌과 커져가는 긴장을 불러일으켰다. 페기는 1차 진료 의사가 여러 차례 방문 동안 똑같이 흔들리지 않는 걱정을 듣고 정신건강 평가를 권한 뒤 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 몇 달째 남편 가족이 하고 있는 일을 사람들이 진지하게 받아들여 주게 하려고 애써왔는데, 그래서 오게 됐어요. 그 사람들이 조용히 우리 돈이랑 평판을 흔들고 있어요. 그러니까, 직장에서 작은 청구 실수가 생기거나, 교회에서 누가 갑자기 저한테 이상하게 행동하거나 하는데, 사람들은 증거가 없다거나 기록에는 아무것도 안 나온다고 해요. 근데 저는 그게 다 그 집안이랑 연결돼 있다는 걸 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 다른 사람들도 남편 가족과 이런 일들 사이의 연관성을 알아차릴 수 있다고 생각하시나요, 아니면 본인만 그걸 눈치채고 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 제가 거의 유일하게 그걸 명확히 보고 있는 것 같아요. 다른 사람들도 조각조각은 눈치채요, 청구 오류라든가 교회에서 누가 다르게 행동하는 거라든가. 근데 그걸 하나로 연결해서 보려고는 안 해요. 기록에는 아무것도 안 나온다고들 하는데, 저는 남편 가족이 그 뒤에 있다는 걸 알아요. 그 사람들은 조심스럽게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 남편 가족이 본인을 향한 행동을 공개적으로 얘기하고 다닌다고 생각하시나요, 아니면 몰래 하고 있는 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 공개적으로 말하지는 않아요. 그게 바로 문제예요—조용히 하고 있어서 겉으로 보면 그냥 작은 실수나 사람들이 괜히 다르게 행동하는 걸로 보여요. 근데 저는 그게 그 사람들 짓이라는 걸 알아요, 특히 돈 문제랑 우리 이름이 사람들 입에 오르내리는 방식을 보면요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 만약 남편 가족에게 직접 물어보면 이런 일들을 했다고 인정할 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 인정하지 않을 거예요. 제가 그냥 지어내는 거라거나 단순한 실수라고 할 거예요, 그래야 조용히 넘어갈 수 있으니까요. 근데 저는 돈 문제랑 사람들이 저를 대하는 방식에서 무슨 일이 있었는지 알고 있고, 그건 다 그 집안으로 이어져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 남편 가족에 대한 본인의 믿음에 대해 의심이 든 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 별로 없어요. 그러니까, 공정하게 다른 사람들 말도 들어보려고 하긴 하는데, 몇 달 동안 이런 일들—청구 오류, 교회에서 사람들이 다르게 행동하는 거, 우리 이름이 오르내리는 거—이 계속되고 나니까 우연으로 느껴지지가 않아요. 기록에 뚜렷하게 안 나와도 저는 여전히 그게 남편 가족이랑 이어져 있다는 걸 알아요. 그 사람들은 그냥 조심스럽게 하는 것뿐이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 아무리 작은 가능성이라도, 이 일들의 배후에 남편 가족이 없을 가능성이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 솔직히 아니요, 그럴 가능성은 별로 없다고 생각해요. 다른 방식으로 보려고 해봤는데, 몇 달째 같은 패턴이에요—작은 청구 문제들, 교회에서 사람들이 이상하게 행동하는 거, 우리 이름에 대해 이런저런 말이 나오는 거요. 누가 기록을 보여주면서 그런 거 안 보인다고 해도, 저는 그게 남편 가족으로 이어진다는 걸 알아요. 그냥 조용히 하고 있는 것뿐이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 남편 가족이 이 일들의 배후에 있다고 믿지 않았던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없어요. 시작된 이후로 계속 저한테는 분명했어요. 몇 달째 그 사람들이 조용히 우리 돈이랑 좋은 평판을 흔들고 있다는 걸 사람들이 이해하게 하려고 애써왔어요. 작은 청구 오류라든가, 교회에서 갑자기 사람들이 저한테 다르게 구는 거요… 누가 기록을 확인해 보고 아무것도 안 보인다고 해도, 저는 여전히 그게 그 사람들이랑 연결돼 있다는 걸 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 남편 가족이 하고 있다고 믿는 일들이 실제로 일어날 수 있는 일이라고 보시나요, 아니면 매우 이례적인 일이라고 보시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 실제로 일어날 수 있는 일이라고 생각해요. 그러니까, 사람들이 돈에 관여하거나, 작은 일들이 잘못되게 만들거나, 다른 사람들에게 당신 이름에 대해 이야기하거나 할 수 있잖아요. 제가 불가능한 얘기를 하는 게 아니에요. 그냥 조용히 이루어지고 있어서, 기록을 봐도 다른 사람들이 알아차리기 힘든 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 남편 가족이 이 일들의 배후에 있다고 믿은 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 이제 아홉 달쯤 됐어요. 돈이랑 명절 기대치 문제로 남편 가족이랑 그 다툼이 있고 나서 시작됐고, 그 이후로 그 사람들이 배후에 있다고 믿게 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 본인은 사실이라고 생각하지만 다른 사람들은 믿기 힘들어할 만한 다른 믿음이 또 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 다른 건 별로 없어요. 주로 남편 가족 관련 이 일이에요. 다른 사람들이 제가 너무 지나치게 생각한다고 여기는 건 알지만, 청구 오류가 생기거나 교회에서 사람들이 저한테 이상하게 구는 걸 보면, 그냥 우연이라고 보기가 힘들어요. 누가 기록을 확인해서 아무것도 없다고 해도, 저는 여전히 그게 그 사람들이랑 연결돼 있다고 믿어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 지난 아홉 달 동안 남편 가족이 이 일들의 배후에 있다는 믿음이 바뀌거나 흔들린 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 아니요, 별로요. 그러니까, 그냥 넘기려고 스스로 다독여본 적은 있을지도 모르는데, 비슷한 일들이 계속 반복돼서 다시 떠올라요. 청구 오류, 교회에서 사람들이 저한테 다르게 구는 거… 다른 사람들이 기록에 안 나온다고 해도 다 남편 가족을 가리키는 것 같아요. 그러니까 딱히 흔들렸다고는 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 남편 가족에 대한 본인의 믿음이 사실이 아닐 가능성을 고려해 본 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 사람들이 계속 제가 틀렸다고 할 때 아주 잠깐씩은요. 그냥 청구 실수일 수도 있고 아니면 교회에서 누가 그날 기분이 안 좋았을 뿐일 수도 있다고 생각해 보려고 했어요. 근데 비슷한 작은 일들이 계속 일어나고, 그게 너무 연관돼 있는 것처럼 느껴져요. 사람들이 무슨 기록을 가져와도, 저는 여전히 그게 남편 가족이 우리 돈이랑 이름을 가지고 문제를 일으키는 것과 이어져 있다고 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 남편 가족 말고 다른 사람들이 본인을 노리거나 감시하고 있다고 느낀 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 그 사람들 말고는 별로 없어요. 그러니까, 교회에서 사람들이 이상하게 굴거나 작은 청구 오류가 생기는 건 있는데, 그게 무작위의 사람들이 저를 감시하거나 쫓아다닌다고는 생각 안 해요. 저한테는 다 남편 가족이 조용히 우리 돈이랑 좋은 평판에 문제를 일으키는 걸로 귀결돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 본인은 완전히 확신하지만 다른 사람들은 동의하지 않았던 생각이나 믿음이 또 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 아니요, 딱히 그런 다른 믿음은 없어요. 주로 남편 가족 관련 이 한 가지예요. 그 사람들이 조용히 우리 돈이랑 평판에 문제를 일으키고 있다고 확신해요—청구 문제라든가 교회에서 사람들이 저를 대하는 방식이요. 다른 사람들은 동의 안 하거나 기록에 안 나온다고 하지만, 저는 그게 그 사람들이랑 연결돼 있다는 걸 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 아홉 달 전 이 일들을 처음 알아차렸을 때부터 남편 가족에 대한 믿음이 조금이라도 바뀌었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 딱히 바뀌진 않았어요. 오히려 이 몇 달 동안 비슷한 일들이 계속 반복되면서—작은 청구 오류, 교회에서 사람들이 다르게 구는 것—더 확신하게 됐어요. 누가 기록을 보여주거나 아무것도 증명 안 된다고 해도, 저는 여전히 그게 남편 가족이 우리 돈이랑 이름을 흔드는 걸로 이어진다는 걸 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 완전히 확신했지만 다른 사람들에게는 이상하거나 있을 법하지 않게 느껴졌던 다른 생각이나 믿음이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 아니요, 다른 건 별로 없어요. 계속 말씀드린 이 상황 그대로예요—남편 가족이 조용히 우리 돈이랑 좋은 이름에 문제를 일으키는 거요. 청구 오류라든가 교회에서 사람들이 저한테 이상하게 구는 거요. 다른 사람들은 기록에 안 나온다고 하지만, 저는 그게 그 사람들이랑 이어져 있다는 걸 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 아홉 달 동안 남편 가족이 이 일들의 배후에 있다는 확신이 약해진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 아니요, 별로 약해지지 않았어요. 사람들이 저처럼 보지 않는다는 건 알고, 기록을 가져와서 증거가 없다고 하는 것도 알지만, 저한테는 여전히 그게 맞아떨어져요. 청구 실수들, 교회에서 사람들이 다르게 구는 거… 저는 여전히 남편 가족이 그 배후에서 조용히 우리 돈이랑 이름에 피해를 주고 있다고 믿어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 다른 사람들은 듣거나 보지 못하는 목소리를 듣거나 뭔가를 본 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그런 목소리나 장면을 본 적은 없어요. 그냥 제 주변에서 일어나는 일들을 눈치채는 것뿐이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 아주 강하게 믿었던 것이 나중에 사실이 아니었던 것으로 밝혀진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그러니까, 사람들이 계속 이게 사실이 아니라거나 기록에 아무것도 안 나온다고 하지만, 저는 여전히 무슨 일이 일어나고 있는지 알아요. 몇 달째 남편 가족이 조용히 우리 돈이랑 평판을 흔들고 있다는 걸 설명하려고 애써왔어요—작은 청구 오류라든가 교회에서 몇몇 사람들이 저한테 이상하게 구는 것처럼요. 그게 나중에 거짓으로 밝혀진 거라고는 생각 안 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 페기와 배우자의 친척들 사이의 관계는 돈, 집안일 분담, 명절 모임에 대한 기대를 둘러싼 다툼 이후 껄끄러워졌다. 그 후 9개월 동안, 평범한 가족 간의 오해와 직장에서의 청구 오류가 페기의 머릿속에서 시댁 식구들이 자신들의 평판과 재정적 안정을 흔들려 한다는 고정된 믿음과 연결되었고, 은행 기록과 동료들, 배우자가 그 반대 증거를 제시해도 흔들리지 않았다. 그 확신이 페기가 평소의 사무직 업무나 정원 가꾸기, 그림 그리기를 하는 것을 막지는 않았지만, 가정과 교회 모임에서 반복적인 충돌과 커져가는 긴장을 불러일으켰다. 페기는 1차 진료 의사가 여러 차례 방문 동안 똑같이 흔들리지 않는 걱정을 듣고 정신건강 평가를 권한 뒤 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -996,11 +1001,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2544</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.2544</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
